--- a/cahier_de_test/Cahier de Tests Unitaires - Gestion des Fraudes.xlsx
+++ b/cahier_de_test/Cahier de Tests Unitaires - Gestion des Fraudes.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titou\OneDrive\Desktop\ESEO\Dev_logiciel\projet_avec_le_gui\ProjetFraude\cahier_de_test\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B76CADF-1890-40F7-9B2D-AB14C72BAD96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Cahier de Tests Unitaires - Ges" sheetId="1" r:id="rId5"/>
+    <sheet name="Cahier de Tests Unitaires - Ges" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="94">
   <si>
     <t>ID Test</t>
   </si>
@@ -224,27 +233,112 @@
   </si>
   <si>
     <t>Si on donne un chemin interdit (ex: . dossier courant), le code gère le try/catch sans faire planter l'application.</t>
+  </si>
+  <si>
+    <t>Tests de la consoleUI et du main pas encore programmés: à faire lors de la prochaine séance.</t>
+  </si>
+  <si>
+    <t>Résultat Obtenu</t>
+  </si>
+  <si>
+    <t>Succès. L'instance est bien créée avec l'ID 1, les noms attendus et le cursus E3e.</t>
+  </si>
+  <si>
+    <t>Validé. Les paramètres modifiés sont correctement assignés et retournés par les getters.</t>
+  </si>
+  <si>
+    <t>Succès. L'objet est instancié avec ses attributs correctement initialisés à null ou 0.</t>
+  </si>
+  <si>
+    <t>OK. Les attributs de l'épreuve correspondent exactement aux paramètres fournis lors de l'instanciation.</t>
+  </si>
+  <si>
+    <t>Succès. Les getters retournent bien les nouvelles valeurs après l'appel systématique des setters.</t>
+  </si>
+  <si>
+    <t>Validé. La méthode values().length retourne 6 et les constantes sont conformes.</t>
+  </si>
+  <si>
+    <t>Succès. L'ID s'auto-incrémente, les dates sont identiques et les listes sont vides sans erreur.</t>
+  </si>
+  <si>
+    <t>OK. Toutes les collections et références passées en paramètres sont correctement stockées.</t>
+  </si>
+  <si>
+    <t>Succès. La taille de la liste passe à 1 et isAfter() confirme la mise à jour de la date de modification.</t>
+  </si>
+  <si>
+    <t>Succès. La fraude est ajoutée à la liste et la date est actualisée de manière identique.</t>
+  </si>
+  <si>
+    <t>Validé. Le booléen estPlie réagit correctement selon le constructeur utilisé.</t>
+  </si>
+  <si>
+    <t>OK. La marque par défaut est bien assignée, et les paramètres surchargent correctement la classe mère.</t>
+  </si>
+  <si>
+    <t>Succès. Le nom du service (vide ou spécifié) est correctement initialisé.</t>
+  </si>
+  <si>
+    <t>Validé. L'adresse IP locale "127.0.0.1" est fixée par défaut, ou remplacée si passée en argument.</t>
+  </si>
+  <si>
+    <t>Succès. L'action est sauvegardée et l'horodatage est automatiquement généré à l'instant T.</t>
+  </si>
+  <si>
+    <t>OK. La lecture des variables écrasées par les setters confirme la modification.</t>
+  </si>
+  <si>
+    <t>Validé. Le journal s'initialise correctement avec une liste d'entrées vide.</t>
+  </si>
+  <si>
+    <t>Succès. La taille de la liste passe à 2 et le contenu correspond aux ajouts.</t>
+  </si>
+  <si>
+    <t>OK. Le setter global écrase bien l'ancienne liste par la nouvelle référence.</t>
+  </si>
+  <si>
+    <t>Succès. Le fichier .txt est généré physiquement puis correctement supprimé lors du teardown du test.</t>
+  </si>
+  <si>
+    <t>Validé. L'exception d'accès au chemin est proprement attrapée, le programme poursuit son exécution.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -252,69 +346,59 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="5">
     <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF356854"/>
-          <bgColor rgb="FF356854"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF6F8F9"/>
-          <bgColor rgb="FFF6F8F9"/>
-        </patternFill>
-      </fill>
-      <border/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
     </dxf>
     <dxf>
       <border>
@@ -332,40 +416,114 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle count="4" pivot="0" name="Cahier de Tests Unitaires - Ges-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    <tableStyle name="Cahier de Tests Unitaires - Ges-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="1"/>
+      <tableStyleElement type="headerRow" dxfId="4"/>
+      <tableStyleElement type="firstRowStripe" dxfId="3"/>
+      <tableStyleElement type="secondRowStripe" dxfId="2"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>361516</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>111485</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>4655421</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>181838</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{610F0CCD-00D3-5A77-A12E-C1AC325B4F7A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1772949" y="6597145"/>
+          <a:ext cx="7783517" cy="2460262"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D22" displayName="Tableau1" name="Tableau1" id="1">
-  <tableColumns count="4">
-    <tableColumn name="ID Test" id="1"/>
-    <tableColumn name="Classe" id="2"/>
-    <tableColumn name="Description du Test" id="3"/>
-    <tableColumn name="Résultat Attendu" id="4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tableau1" displayName="Tableau1" ref="A1:E22">
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID Test"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Classe"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description du Test"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Résultat Attendu"/>
+    <tableColumn id="5" xr3:uid="{0E5BD603-9E07-422C-8CB7-D79F7ECC2025}" name="Résultat Obtenu" dataDxfId="0"/>
   </tableColumns>
-  <tableStyleInfo name="Cahier de Tests Unitaires - Ges-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Cahier de Tests Unitaires - Ges-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -555,24 +713,28 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F37"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="19.75"/>
-    <col customWidth="1" min="2" max="2" width="18.0"/>
-    <col customWidth="1" min="3" max="3" width="30.75"/>
-    <col customWidth="1" min="4" max="4" width="104.5"/>
+    <col min="1" max="1" width="19.73046875" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="30.73046875" customWidth="1"/>
+    <col min="4" max="4" width="104.46484375" customWidth="1"/>
+    <col min="5" max="5" width="87.06640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1">
+    <row r="1" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -585,8 +747,11 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" ht="22.5" customHeight="1">
+      <c r="E1" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -599,8 +764,11 @@
       <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" ht="22.5" customHeight="1">
+      <c r="E2" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -613,8 +781,11 @@
       <c r="D3" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" ht="22.5" customHeight="1">
+      <c r="E3" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
@@ -627,8 +798,11 @@
       <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" ht="22.5" customHeight="1">
+      <c r="E4" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
@@ -641,8 +815,11 @@
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" ht="22.5" customHeight="1">
+      <c r="E5" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
@@ -655,8 +832,11 @@
       <c r="D6" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" ht="22.5" customHeight="1">
+      <c r="E6" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>19</v>
       </c>
@@ -669,8 +849,11 @@
       <c r="D7" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" ht="22.5" customHeight="1">
+      <c r="E7" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>22</v>
       </c>
@@ -683,8 +866,11 @@
       <c r="D8" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="9" ht="22.5" customHeight="1">
+      <c r="E8" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>26</v>
       </c>
@@ -697,8 +883,11 @@
       <c r="D9" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="10" ht="22.5" customHeight="1">
+      <c r="E9" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>29</v>
       </c>
@@ -711,8 +900,11 @@
       <c r="D10" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="11" ht="22.5" customHeight="1">
+      <c r="E10" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>32</v>
       </c>
@@ -725,8 +917,11 @@
       <c r="D11" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="12" ht="22.5" customHeight="1">
+      <c r="E11" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>35</v>
       </c>
@@ -739,8 +934,11 @@
       <c r="D12" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="13" ht="22.5" customHeight="1">
+      <c r="E12" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>39</v>
       </c>
@@ -753,8 +951,11 @@
       <c r="D13" s="2" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="14" ht="22.5" customHeight="1">
+      <c r="E13" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="2" t="s">
         <v>42</v>
       </c>
@@ -767,8 +968,12 @@
       <c r="D14" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="15" ht="22.5" customHeight="1">
+      <c r="E14" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>45</v>
       </c>
@@ -781,8 +986,11 @@
       <c r="D15" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="16" ht="22.5" customHeight="1">
+      <c r="E15" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>48</v>
       </c>
@@ -795,8 +1003,11 @@
       <c r="D16" s="2" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="17" ht="22.5" customHeight="1">
+      <c r="E16" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>52</v>
       </c>
@@ -809,8 +1020,11 @@
       <c r="D17" s="2" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="18" ht="22.5" customHeight="1">
+      <c r="E17" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>55</v>
       </c>
@@ -823,8 +1037,11 @@
       <c r="D18" s="2" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="19" ht="22.5" customHeight="1">
+      <c r="E18" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>59</v>
       </c>
@@ -837,8 +1054,11 @@
       <c r="D19" s="2" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="20" ht="22.5" customHeight="1">
+      <c r="E19" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>62</v>
       </c>
@@ -851,8 +1071,11 @@
       <c r="D20" s="2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="21" ht="22.5" customHeight="1">
+      <c r="E20" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>65</v>
       </c>
@@ -865,8 +1088,11 @@
       <c r="D21" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="22" ht="22.5" customHeight="1">
+      <c r="E21" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>68</v>
       </c>
@@ -879,12 +1105,20 @@
       <c r="D22" s="2" t="s">
         <v>70</v>
       </c>
+      <c r="E22" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="37" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C37" t="s">
+        <v>71</v>
+      </c>
     </row>
   </sheetData>
-  <printOptions gridLines="1" horizontalCentered="1"/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup fitToHeight="0" paperSize="9" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
-  <drawing r:id="rId1"/>
+  <printOptions horizontalCentered="1" gridLines="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd" r:id="rId1"/>
+  <drawing r:id="rId2"/>
   <tableParts count="1">
     <tablePart r:id="rId3"/>
   </tableParts>

--- a/cahier_de_test/Cahier de Tests Unitaires - Gestion des Fraudes.xlsx
+++ b/cahier_de_test/Cahier de Tests Unitaires - Gestion des Fraudes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\titou\OneDrive\Desktop\ESEO\Dev_logiciel\projet_avec_le_gui\ProjetFraude\cahier_de_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B76CADF-1890-40F7-9B2D-AB14C72BAD96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC03651-1FFE-4E29-9CDF-B24A440C24A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="153">
   <si>
     <t>ID Test</t>
   </si>
@@ -235,9 +235,6 @@
     <t>Si on donne un chemin interdit (ex: . dossier courant), le code gère le try/catch sans faire planter l'application.</t>
   </si>
   <si>
-    <t>Tests de la consoleUI et du main pas encore programmés: à faire lors de la prochaine séance.</t>
-  </si>
-  <si>
     <t>Résultat Obtenu</t>
   </si>
   <si>
@@ -302,13 +299,472 @@
   </si>
   <si>
     <t>Validé. L'exception d'accès au chemin est proprement attrapée, le programme poursuit son exécution.</t>
+  </si>
+  <si>
+    <t>TEST-ETU-03</t>
+  </si>
+  <si>
+    <t>Méthodes equals() et hashCode()</t>
+  </si>
+  <si>
+    <t>TEST-SYS-01</t>
+  </si>
+  <si>
+    <t>TEST-SYS-02</t>
+  </si>
+  <si>
+    <t>TEST-SYS-03</t>
+  </si>
+  <si>
+    <t>TEST-SYS-04</t>
+  </si>
+  <si>
+    <t>TEST-SYS-05</t>
+  </si>
+  <si>
+    <t>TEST-SYS-06</t>
+  </si>
+  <si>
+    <t>TEST-SYS-07</t>
+  </si>
+  <si>
+    <t>TEST-UI-01</t>
+  </si>
+  <si>
+    <t>TEST-UI-02</t>
+  </si>
+  <si>
+    <t>TEST-UI-03</t>
+  </si>
+  <si>
+    <t>TEST-UI-04</t>
+  </si>
+  <si>
+    <t>TEST-UI-05</t>
+  </si>
+  <si>
+    <t>TEST-MAIN-01</t>
+  </si>
+  <si>
+    <t>Main</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Méthodes </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>main()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> et </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>initialiserDonneesTest()</t>
+    </r>
+  </si>
+  <si>
+    <t>L'égalité entre deux étudiants se base uniquement sur le numéro apprenant. Deux instances différentes avec le même ID doivent fusionner.</t>
+  </si>
+  <si>
+    <t>Succès. Les étudiants ayant le même ID retournent true à l'égalité et ont le même hash, permettant au graphe de fonctionner.</t>
+  </si>
+  <si>
+    <t>SystemeGestion</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Méthode </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>enregistrerFormulaire()</t>
+    </r>
+  </si>
+  <si>
+    <t>L'enregistrement d'un formulaire valide l'ajoute à la liste, met à jour la liste globale des étudiants et crée une trace dans l'historique. Un cas null est ignoré.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Validé. Les listes s'incrémentent correctement et l'historique est tracé. L'insertion d'un </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>null</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ne fait pas planter le système.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Méthode </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>supprimerFormulaire()</t>
+    </r>
+  </si>
+  <si>
+    <t>La suppression via un ID valide retire le bon formulaire. Un ID inexistant lève proprement l'exception métier personnalisée.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Succès. La suppression fonctionne et l'exception </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>FraudeException</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> est proprement levée et attrapée en cas de mauvais ID.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Méthodes de recherche (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>trouver...</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> et </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>rechercheCroisee</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Les recherches par étudiant (ID ou Nom/Prénom), par épreuve (ECUE) et croisées (Cursus + Type Fraude) filtrent correctement les formulaires.</t>
+  </si>
+  <si>
+    <t>OK. Les listes retournées contiennent exactement les objets correspondant aux différents critères de recherche appliqués.</t>
+  </si>
+  <si>
+    <t>Interface IAnalyseStatistique</t>
+  </si>
+  <si>
+    <t>Les calculs statistiques renvoient les bonnes mathématiques (Moyennes, Écart-types, Cumuls). La division par zéro est évitée si le système est vide.</t>
+  </si>
+  <si>
+    <t>Validé. Les calculs sont exacts (vérifiés au millième près). Le système totalement vide renvoie proprement 0.0.</t>
+  </si>
+  <si>
+    <r>
+      <t>Algorithmique (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>genererGraphe...</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> et </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>trouverCerveau...</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>L'algorithme du graphe lie correctement les complices d'un même dossier et ignore les doublons en mémoire. Le "cerveau" renvoyé est bien l'étudiant avec le plus de voisins.</t>
+  </si>
+  <si>
+    <t>Succès. Le graphe fusionne les doublons. L'étudiant au centre de plusieurs dossiers croisés est bien élu "cerveau".</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Méthodes </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>sauvegarder()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> et </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>charger()</t>
+    </r>
+  </si>
+  <si>
+    <t>La persistance des données génère un fichier binaire lisible. Les données rechargées correspondent exactement à l'état préalablement sauvegardé.</t>
+  </si>
+  <si>
+    <t>OK. Sérialisation et désérialisation fonctionnelles. Le fichier physique .dat est généré puis proprement supprimé par le test.</t>
+  </si>
+  <si>
+    <t>Gestion des Exceptions d'Entrées/Sorties</t>
+  </si>
+  <si>
+    <t>Le système gère les erreurs de fichiers (fichier fantôme, chemin interdit, fichier texte corrompu à la place d'un binaire).</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Validé. Les </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>IOException</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> et </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>ClassNotFoundException</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sont attrapées. Le système s'initialise à vide sans crasher.</t>
+    </r>
+  </si>
+  <si>
+    <t>ConsoleUI</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Méthode </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>demarrer()</t>
+    </r>
+  </si>
+  <si>
+    <t>La boucle principale du menu gère les mauvaises saisies (lettres, chiffres hors limites) sans planter et se termine bien via l'option Quitter (10).</t>
+  </si>
+  <si>
+    <t>Succès. Les flux injectés via ByteArrayInputStream naviguent dans le menu en ignorant les erreurs de saisie.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Méthode </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>saisirNouveauFormulaire()</t>
+    </r>
+  </si>
+  <si>
+    <t>La saisie complète d'un dossier gère les formats de date/heure invalides saisis par l'utilisateur en appliquant des valeurs par défaut.</t>
+  </si>
+  <si>
+    <t>OK. Le formulaire est correctement créé avec les valeurs par défaut lorsque les entrées clavier sont incorrectes.</t>
+  </si>
+  <si>
+    <t>Méthodes selectionnerModalite() et selectionnerCursus()</t>
+  </si>
+  <si>
+    <t>Les switch-cases des sous-menus parcourent correctement l'intégralité des Énumérations (Cursus E1 à E5, et toutes les Modalités d'épreuve).</t>
+  </si>
+  <si>
+    <t>Validé. Tous les cas de figures clavier (1 à 6) sont couverts par les tests et renvoient les bonnes constantes énumérées.</t>
+  </si>
+  <si>
+    <t>Méthodes d'affichages et d'analyse</t>
+  </si>
+  <si>
+    <t>L'affichage textuel des données (Liste des dossiers, Historique, Statistiques, Graphe) s'exécute correctement sans crash, même si le système est totalement vide.</t>
+  </si>
+  <si>
+    <t>Succès. L'interface affiche les messages "Aucun dossier" ou "Réseau vide" sans jamais lever de NullPointerException.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Méthode </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>testScenarioReseauComplet()</t>
+    </r>
+  </si>
+  <si>
+    <t>Test de bout en bout (End-to-End) : Saisie séquentielle de plusieurs dossiers impliquant des complices croisés, puis lancement de l'analyse réseau via l'UI.</t>
+  </si>
+  <si>
+    <t>Validé. Le test E2E confirme que l'interface remplit correctement les données compliquées jusqu'à la détection exacte du cerveau.</t>
+  </si>
+  <si>
+    <t>L'initialisation du programme charge le jeu de données de test (Bouchonnage) si aucune sauvegarde n'existe sur le disque.</t>
+  </si>
+  <si>
+    <t>Succès. Les 4 étudiants, 2 épreuves et 3 formulaires exigés par le cahier des charges sont bien injectés au démarrage du programme.</t>
+  </si>
+  <si>
+    <t>Test de certaines classes à retravailler pour atteindre au moins les 80% (demandé dans le cahier des charges)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -340,6 +796,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -361,7 +838,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -376,6 +853,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -399,22 +879,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF356854"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF356854"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF356854"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF356854"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <fill>
@@ -440,13 +904,29 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Cahier de Tests Unitaires - Ges-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="1"/>
-      <tableStyleElement type="headerRow" dxfId="4"/>
-      <tableStyleElement type="firstRowStripe" dxfId="3"/>
-      <tableStyleElement type="secondRowStripe" dxfId="2"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="4"/>
+      <tableStyleElement type="headerRow" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="secondRowStripe" dxfId="1"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -464,23 +944,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>361516</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>111485</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2974859</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>135798</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>4655421</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>181838</xdr:rowOff>
+      <xdr:colOff>7364866</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>18805</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Image 1">
+        <xdr:cNvPr id="3" name="Image 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{610F0CCD-00D3-5A77-A12E-C1AC325B4F7A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93555E24-6360-62C0-C5D9-2E742230BAE2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -496,8 +976,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1772949" y="6597145"/>
-          <a:ext cx="7783517" cy="2460262"/>
+          <a:off x="5665672" y="9255986"/>
+          <a:ext cx="7699944" cy="3323914"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -510,7 +990,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tableau1" displayName="Tableau1" ref="A1:E22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tableau1" displayName="Tableau1" ref="A1:E36">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID Test"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Classe"/>
@@ -724,14 +1204,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.73046875" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="30.73046875" customWidth="1"/>
-    <col min="4" max="4" width="104.46484375" customWidth="1"/>
-    <col min="5" max="5" width="87.06640625" customWidth="1"/>
+    <col min="3" max="3" width="46.265625" customWidth="1"/>
+    <col min="4" max="4" width="141.3984375" customWidth="1"/>
+    <col min="5" max="5" width="111.46484375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -741,14 +1221,14 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -765,7 +1245,7 @@
         <v>7</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -782,342 +1262,580 @@
         <v>10</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>13</v>
+      <c r="A4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F14" s="4"/>
     </row>
     <row r="15" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E22" s="5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="37" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C37" t="s">
-        <v>71</v>
+      <c r="E23" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A24" t="s">
+        <v>95</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A25" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A26" t="s">
+        <v>97</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>98</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A28" t="s">
+        <v>99</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A29" t="s">
+        <v>100</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A30" t="s">
+        <v>101</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A31" t="s">
+        <v>102</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>104</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>105</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A35" t="s">
+        <v>106</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A36" t="s">
+        <v>107</v>
+      </c>
+      <c r="B36" t="s">
+        <v>108</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="54" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D54" s="5" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="39" fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd" r:id="rId1"/>
   <drawing r:id="rId2"/>
   <tableParts count="1">
     <tablePart r:id="rId3"/>
